--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128612051</v>
+        <v>128612968</v>
       </c>
       <c r="B2" t="n">
         <v>79083</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462244</v>
+        <v>462205</v>
       </c>
       <c r="R2" t="n">
-        <v>6794651</v>
+        <v>6794627</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128612680</v>
+        <v>128612051</v>
       </c>
       <c r="B3" t="n">
         <v>79083</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462141</v>
+        <v>462244</v>
       </c>
       <c r="R3" t="n">
-        <v>6794596</v>
+        <v>6794651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128612212</v>
+        <v>128612680</v>
       </c>
       <c r="B4" t="n">
         <v>79083</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462227</v>
+        <v>462141</v>
       </c>
       <c r="R4" t="n">
-        <v>6794650</v>
+        <v>6794596</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,11 +970,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bild 3, garn på stam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128612217</v>
+        <v>128612471</v>
       </c>
       <c r="B5" t="n">
         <v>79083</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462217</v>
+        <v>462183</v>
       </c>
       <c r="R5" t="n">
-        <v>6794660</v>
+        <v>6794647</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,6 +1077,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bild 6, garn på stam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128612471</v>
+        <v>128612549</v>
       </c>
       <c r="B6" t="n">
         <v>79083</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462183</v>
+        <v>462161</v>
       </c>
       <c r="R6" t="n">
-        <v>6794647</v>
+        <v>6794600</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,11 +1189,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bild 6, garn på stam</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128612549</v>
+        <v>128612212</v>
       </c>
       <c r="B7" t="n">
         <v>79083</v>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462161</v>
+        <v>462227</v>
       </c>
       <c r="R7" t="n">
-        <v>6794600</v>
+        <v>6794650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,6 +1296,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bild 3, garn på stam</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128612142</v>
+        <v>128612217</v>
       </c>
       <c r="B8" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462227</v>
+        <v>462217</v>
       </c>
       <c r="R8" t="n">
-        <v>6794650</v>
+        <v>6794660</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,11 +1408,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Område 2, bild 1, stubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128612391</v>
+        <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462193</v>
+        <v>462227</v>
       </c>
       <c r="R9" t="n">
-        <v>6794653</v>
+        <v>6794650</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,6 +1515,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Område 2, bild 1, stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128612767</v>
+        <v>128613170</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1557,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Böån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462180</v>
+        <v>462232</v>
       </c>
       <c r="R10" t="n">
-        <v>6794613</v>
+        <v>6794609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1627,6 +1632,11 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bild 11,</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128612874</v>
+        <v>128612391</v>
       </c>
       <c r="B11" t="n">
         <v>79083</v>
@@ -1688,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462205</v>
+        <v>462193</v>
       </c>
       <c r="R11" t="n">
-        <v>6794627</v>
+        <v>6794653</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1757,6 +1767,765 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128612767</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>462180</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6794613</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128613076</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>462220</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6794616</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128613044</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>462210</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6794614</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128613396</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>462253</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6794628</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bild 13, garn på flera stammar</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128613288</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>462252</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6794619</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128613188</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>462232</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6794609</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128613276</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>462243</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6794612</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bild 12 på stam</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128612471</v>
+        <v>128612549</v>
       </c>
       <c r="B5" t="n">
         <v>79083</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462183</v>
+        <v>462161</v>
       </c>
       <c r="R5" t="n">
-        <v>6794647</v>
+        <v>6794600</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,11 +1077,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bild 6, garn på stam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128612549</v>
+        <v>128612471</v>
       </c>
       <c r="B6" t="n">
         <v>79083</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462161</v>
+        <v>462183</v>
       </c>
       <c r="R6" t="n">
-        <v>6794600</v>
+        <v>6794647</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,6 +1184,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bild 6, garn på stam</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612968</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128612051</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128612680</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128612549</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128612471</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128612217</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128613170</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128612391</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128612767</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>128613076</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128613044</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128613288</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>128613188</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612968</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128612051</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128612680</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128612549</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128612471</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128612217</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128612391</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128612767</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>128613076</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128613044</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128613288</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>128613188</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612968</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128612051</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128612680</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128612549</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128612471</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128612217</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128613170</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128612391</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128612767</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>128613076</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128613044</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128613288</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>128613188</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612968</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128612051</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128612680</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128612549</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128612471</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128612217</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128612391</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128612767</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>128613076</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128613044</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128613288</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>128613188</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612968</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128612051</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128612680</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128612549</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128612471</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128612217</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128613170</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128612391</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128612767</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>128613076</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128613044</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128613288</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>128613188</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612968</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128612051</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128612680</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128612549</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128612471</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128612217</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128613170</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128612391</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128612767</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>128613076</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128613044</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128613288</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>128613188</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612968</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128612051</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128612680</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128612549</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128612471</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128612217</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128612391</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128612767</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>128613076</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128613044</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128613288</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>128613188</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128612968</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128612051</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128612680</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128612549</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128612471</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>128612217</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>128612391</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>128612767</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>128613076</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128613044</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128613288</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>128613188</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128613170</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128612212</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>128612142</v>
       </c>
       <c r="B9" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>128613170</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>128613396</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128613276</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128612968</v>
+        <v>128609310</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462205</v>
+        <v>462211</v>
       </c>
       <c r="R2" t="n">
-        <v>6794627</v>
+        <v>6794680</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,14 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128612051</v>
+        <v>128609337</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -889,14 +894,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128612680</v>
+        <v>128612195</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462141</v>
+        <v>462227</v>
       </c>
       <c r="R4" t="n">
-        <v>6794596</v>
+        <v>6794650</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,6 +975,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bild 2, garn på stam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,14 +1006,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128612549</v>
+        <v>128612217</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1031,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462161</v>
+        <v>462217</v>
       </c>
       <c r="R5" t="n">
-        <v>6794600</v>
+        <v>6794660</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,14 +1113,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128612471</v>
+        <v>128612260</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1138,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462183</v>
+        <v>462213</v>
       </c>
       <c r="R6" t="n">
-        <v>6794647</v>
+        <v>6794674</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1194,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bild 6, garn på stam</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,14 +1220,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128612212</v>
+        <v>128612357</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1250,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462227</v>
+        <v>462196</v>
       </c>
       <c r="R7" t="n">
-        <v>6794650</v>
+        <v>6794669</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Bild 3, garn på stam</t>
+          <t>Bild 4, garn på stam</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,14 +1332,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128612217</v>
+        <v>128612391</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1362,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462217</v>
+        <v>462193</v>
       </c>
       <c r="R8" t="n">
-        <v>6794660</v>
+        <v>6794653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,32 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128612142</v>
+        <v>128612438</v>
       </c>
       <c r="B9" t="n">
-        <v>79660</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462227</v>
+        <v>462183</v>
       </c>
       <c r="R9" t="n">
-        <v>6794650</v>
+        <v>6794647</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,11 +1520,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Område 2, bild 1, stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,50 +1546,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128613170</v>
+        <v>128612542</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Böån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462232</v>
+        <v>462161</v>
       </c>
       <c r="R10" t="n">
-        <v>6794609</v>
+        <v>6794600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1636,7 +1631,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Bild 11,</t>
+          <t>Bild 7, garn på stam</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,14 +1658,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128612391</v>
+        <v>128612680</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1698,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462193</v>
+        <v>462141</v>
       </c>
       <c r="R11" t="n">
-        <v>6794653</v>
+        <v>6794596</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,14 +1765,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128612767</v>
+        <v>128612704</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1805,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462180</v>
+        <v>462134</v>
       </c>
       <c r="R12" t="n">
-        <v>6794613</v>
+        <v>6794588</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1825,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1877,14 +1872,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128613076</v>
+        <v>128612767</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1912,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462220</v>
+        <v>462180</v>
       </c>
       <c r="R13" t="n">
-        <v>6794616</v>
+        <v>6794613</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1984,14 +1979,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128613044</v>
+        <v>128612874</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2019,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>462210</v>
+        <v>462205</v>
       </c>
       <c r="R14" t="n">
-        <v>6794614</v>
+        <v>6794627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,14 +2086,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128613396</v>
+        <v>128613013</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2126,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>462253</v>
+        <v>462183</v>
       </c>
       <c r="R15" t="n">
-        <v>6794628</v>
+        <v>6794597</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2146,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2172,11 +2167,6 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Bild 13, garn på flera stammar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2203,14 +2193,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128613288</v>
+        <v>128613044</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2238,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462252</v>
+        <v>462210</v>
       </c>
       <c r="R16" t="n">
-        <v>6794619</v>
+        <v>6794614</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2310,14 +2300,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128613188</v>
+        <v>128613076</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2345,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462232</v>
+        <v>462220</v>
       </c>
       <c r="R17" t="n">
-        <v>6794609</v>
+        <v>6794616</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,7 +2360,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Våmhus</t>
+          <t>Mora</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2417,14 +2407,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128613276</v>
+        <v>128613188</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2452,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462243</v>
+        <v>462232</v>
       </c>
       <c r="R18" t="n">
-        <v>6794612</v>
+        <v>6794609</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2467,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Mora</t>
+          <t>Våmhus</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2498,11 +2488,6 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Bild 12 på stam</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2526,6 +2511,678 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128613276</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>462243</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6794612</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bild 12 på stam</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128613288</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>462252</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6794619</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128613396</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>462253</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6794628</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bild 13, garn på flera stammar</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128612142</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>462227</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6794650</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Område 2, bild 1, stubbe</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128612702</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>462134</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6794588</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128613170</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Böån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>462232</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6794609</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bild 11,</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39481-2025 artfynd.xlsx
+++ b/artfynd/A 39481-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128609310</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128609337</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612195</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612217</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612260</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612357</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612391</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612438</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612542</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612680</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612704</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612767</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2083,6 +2148,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612874</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2190,6 +2260,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128613013</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2297,6 +2372,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128613044</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2404,6 +2484,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128613076</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2511,6 +2596,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128613188</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2623,6 +2713,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128613276</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2730,6 +2825,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128613288</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2842,6 +2942,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128613396</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2954,6 +3059,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612142</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3066,6 +3176,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128612702</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3183,8 +3298,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128613170</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>